--- a/reiting1.xlsx
+++ b/reiting1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4F8FB0F-DB96-49ED-8A7C-85FE2F7F28BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C183829-22EB-4B1A-9377-17C1C6F0D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4125" yWindow="225" windowWidth="16365" windowHeight="10695" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
   </bookViews>
@@ -159,9 +159,6 @@
     <t>КОЖАГЕЛЬДИНОВА</t>
   </si>
   <si>
-    <t>МОМЫНОВ</t>
-  </si>
-  <si>
     <t>Химия</t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>Информатика</t>
+  </si>
+  <si>
+    <t>МОМЫНОВ Қуат</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
         <v>32</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -1043,7 +1043,7 @@
         <v>34</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" s="6">
         <v>0.9</v>
@@ -1115,7 +1115,7 @@
         <v>35</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="6">
         <v>1.1000000000000001</v>
@@ -1187,7 +1187,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="6">
         <v>0.9</v>
@@ -1259,7 +1259,7 @@
         <v>38</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -1331,7 +1331,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D10" s="6">
         <v>0.8</v>
@@ -1403,7 +1403,7 @@
         <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D11" s="6">
         <v>0.9</v>
@@ -1475,7 +1475,7 @@
         <v>41</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="6">
         <v>1.1000000000000001</v>
@@ -1547,7 +1547,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="6">
         <v>0.6</v>
@@ -1688,10 +1688,10 @@
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>

--- a/reiting1.xlsx
+++ b/reiting1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C183829-22EB-4B1A-9377-17C1C6F0D38C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF47736-D80F-47F5-9B01-A8DE0317E948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4125" yWindow="225" windowWidth="16365" windowHeight="10695" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
   </bookViews>
@@ -345,7 +345,6 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -354,6 +353,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -683,61 +683,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="15" t="s">
+      <c r="A1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="C1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12" t="s">
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12" t="s">
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12" t="s">
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12" t="s">
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
     </row>
     <row r="2" spans="1:32" s="1" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="14"/>
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="13"/>
       <c r="E2" s="4" t="s">
         <v>6</v>
       </c>
@@ -842,35 +842,65 @@
         <f>SUM(E3-D3-F3)</f>
         <v>-7.8000000000000007</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="H3" s="6">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>3</v>
+      </c>
+      <c r="J3" s="6">
+        <v>1</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1</v>
+      </c>
       <c r="L3" s="8">
         <f>SUM(H3+I3+J3+K3)</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="M3" s="6">
+        <v>1</v>
+      </c>
+      <c r="N3" s="6">
+        <v>1</v>
+      </c>
+      <c r="O3" s="6">
+        <v>4</v>
+      </c>
+      <c r="P3" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>2</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3</v>
+      </c>
       <c r="S3" s="9">
         <f>SUM(M3+N3+O3+P3+Q3+R3)</f>
-        <v>0</v>
-      </c>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="T3" s="6">
+        <v>2</v>
+      </c>
+      <c r="U3" s="6">
+        <v>4</v>
+      </c>
+      <c r="V3" s="6">
+        <v>2</v>
+      </c>
+      <c r="W3" s="6">
+        <v>3</v>
+      </c>
+      <c r="X3" s="6">
+        <v>3</v>
+      </c>
       <c r="Y3" s="6">
         <v>-6</v>
       </c>
       <c r="Z3" s="10">
         <f>SUM(T3+U3+V3+W3+X3+Y3)</f>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="AA3" s="7">
         <f>SUM(G3)</f>
@@ -878,19 +908,19 @@
       </c>
       <c r="AB3" s="8">
         <f>SUM(L3)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="9">
         <f>SUM(S3)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD3" s="10">
         <f>SUM(Z3)</f>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="AE3" s="11">
         <f>SUM(G3+L3+S3+Z3)</f>
-        <v>-13.8</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.25">
@@ -914,35 +944,65 @@
         <f t="shared" ref="G4:G15" si="0">SUM(E4-D4-F4)</f>
         <v>-4.5</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="H4" s="6">
+        <v>1</v>
+      </c>
+      <c r="I4" s="6">
+        <v>2</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="K4" s="6">
+        <v>2</v>
+      </c>
       <c r="L4" s="8">
         <f t="shared" ref="L4:L15" si="1">SUM(H4+I4+J4+K4)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="M4" s="6">
+        <v>1</v>
+      </c>
+      <c r="N4" s="6">
+        <v>1</v>
+      </c>
+      <c r="O4" s="6">
+        <v>4</v>
+      </c>
+      <c r="P4" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>3</v>
+      </c>
+      <c r="R4" s="6">
+        <v>3</v>
+      </c>
       <c r="S4" s="9">
         <f t="shared" ref="S4:S15" si="2">SUM(M4+N4+O4+P4+Q4+R4)</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="T4" s="6">
+        <v>2</v>
+      </c>
+      <c r="U4" s="6">
+        <v>2</v>
+      </c>
+      <c r="V4" s="6">
+        <v>3</v>
+      </c>
+      <c r="W4" s="6">
+        <v>3</v>
+      </c>
+      <c r="X4" s="6">
+        <v>3</v>
+      </c>
       <c r="Y4" s="6">
         <v>-6</v>
       </c>
       <c r="Z4" s="10">
         <f t="shared" ref="Z4:Z15" si="3">SUM(T4+U4+V4+W4+X4+Y4)</f>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="7">
         <f t="shared" ref="AA4:AA15" si="4">SUM(G4)</f>
@@ -950,19 +1010,19 @@
       </c>
       <c r="AB4" s="8">
         <f t="shared" ref="AB4:AB15" si="5">SUM(L4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC4" s="9">
         <f t="shared" ref="AC4:AC15" si="6">SUM(S4)</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD4" s="10">
         <f t="shared" ref="AD4:AD15" si="7">SUM(Z4)</f>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AE4" s="11">
         <f t="shared" ref="AE4:AE15" si="8">SUM(G4+L4+S4+Z4)</f>
-        <v>-10.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.25">
@@ -986,35 +1046,65 @@
         <f t="shared" si="0"/>
         <v>-5.4</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="H5" s="6">
+        <v>2</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1</v>
+      </c>
       <c r="L5" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M5" s="6">
+        <v>3</v>
+      </c>
+      <c r="N5" s="6">
+        <v>2</v>
+      </c>
+      <c r="O5" s="6">
+        <v>4</v>
+      </c>
+      <c r="P5" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>2</v>
+      </c>
+      <c r="R5" s="6">
+        <v>3</v>
+      </c>
       <c r="S5" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="T5" s="6">
+        <v>2</v>
+      </c>
+      <c r="U5" s="6">
+        <v>3</v>
+      </c>
+      <c r="V5" s="6">
+        <v>2</v>
+      </c>
+      <c r="W5" s="6">
+        <v>3</v>
+      </c>
+      <c r="X5" s="6">
+        <v>3</v>
+      </c>
       <c r="Y5" s="6">
         <v>-6</v>
       </c>
       <c r="Z5" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="7">
         <f t="shared" si="4"/>
@@ -1022,19 +1112,19 @@
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD5" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AE5" s="11">
         <f t="shared" si="8"/>
-        <v>-11.4</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.25">
@@ -1058,35 +1148,65 @@
         <f t="shared" si="0"/>
         <v>-1.1000000000000001</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
       <c r="L6" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M6" s="6">
+        <v>3</v>
+      </c>
+      <c r="N6" s="6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="6">
+        <v>4</v>
+      </c>
+      <c r="P6" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>3</v>
+      </c>
+      <c r="R6" s="6">
+        <v>2</v>
+      </c>
       <c r="S6" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
+        <v>18</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1</v>
+      </c>
+      <c r="U6" s="6">
+        <v>4</v>
+      </c>
+      <c r="V6" s="6">
+        <v>3</v>
+      </c>
+      <c r="W6" s="6">
+        <v>3</v>
+      </c>
+      <c r="X6" s="6">
+        <v>3</v>
+      </c>
       <c r="Y6" s="6">
         <v>-6</v>
       </c>
       <c r="Z6" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="AA6" s="7">
         <f t="shared" si="4"/>
@@ -1094,19 +1214,19 @@
       </c>
       <c r="AB6" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC6" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AD6" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>8</v>
       </c>
       <c r="AE6" s="11">
         <f t="shared" si="8"/>
-        <v>-7.1</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.25">
@@ -1130,35 +1250,63 @@
         <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="H7" s="6">
+        <v>2</v>
+      </c>
+      <c r="I7" s="6">
+        <v>2</v>
+      </c>
+      <c r="J7" s="6">
+        <v>2</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
       <c r="L7" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
+      <c r="N7" s="6">
+        <v>4</v>
+      </c>
+      <c r="O7" s="6">
+        <v>4</v>
+      </c>
+      <c r="P7" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>2</v>
+      </c>
+      <c r="R7" s="6">
+        <v>3</v>
+      </c>
       <c r="S7" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="T7" s="6">
+        <v>2</v>
+      </c>
+      <c r="U7" s="6">
+        <v>2</v>
+      </c>
+      <c r="V7" s="6">
+        <v>2</v>
+      </c>
+      <c r="W7" s="6">
+        <v>3</v>
+      </c>
+      <c r="X7" s="6">
+        <v>3</v>
+      </c>
       <c r="Y7" s="6">
         <v>-6</v>
       </c>
       <c r="Z7" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="4"/>
@@ -1166,19 +1314,19 @@
       </c>
       <c r="AB7" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC7" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD7" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="AE7" s="11">
         <f t="shared" si="8"/>
-        <v>-5.4</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
@@ -1202,35 +1350,65 @@
         <f t="shared" si="0"/>
         <v>-0.19999999999999973</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="H8" s="6">
+        <v>2</v>
+      </c>
+      <c r="I8" s="6">
+        <v>2</v>
+      </c>
+      <c r="J8" s="6">
+        <v>1</v>
+      </c>
+      <c r="K8" s="6">
+        <v>2</v>
+      </c>
       <c r="L8" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="M8" s="6">
+        <v>3</v>
+      </c>
+      <c r="N8" s="6">
+        <v>1</v>
+      </c>
+      <c r="O8" s="6">
+        <v>4</v>
+      </c>
+      <c r="P8" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>2</v>
+      </c>
+      <c r="R8" s="6">
+        <v>2</v>
+      </c>
       <c r="S8" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6"/>
+        <v>14</v>
+      </c>
+      <c r="T8" s="6">
+        <v>2</v>
+      </c>
+      <c r="U8" s="6">
+        <v>3</v>
+      </c>
+      <c r="V8" s="6">
+        <v>3</v>
+      </c>
+      <c r="W8" s="6">
+        <v>3</v>
+      </c>
+      <c r="X8" s="6">
+        <v>2</v>
+      </c>
       <c r="Y8" s="6">
         <v>-6</v>
       </c>
       <c r="Z8" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="7">
         <f t="shared" si="4"/>
@@ -1238,19 +1416,19 @@
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC8" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD8" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AE8" s="11">
         <f t="shared" si="8"/>
-        <v>-6.1999999999999993</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
@@ -1274,35 +1452,65 @@
         <f t="shared" si="0"/>
         <v>-3.4000000000000004</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="H9" s="6">
+        <v>3</v>
+      </c>
+      <c r="I9" s="6">
+        <v>2</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="6">
+        <v>3</v>
+      </c>
       <c r="L9" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
+        <v>9</v>
+      </c>
+      <c r="M9" s="6">
+        <v>3</v>
+      </c>
+      <c r="N9" s="6">
+        <v>2</v>
+      </c>
+      <c r="O9" s="6">
+        <v>4</v>
+      </c>
+      <c r="P9" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="6">
+        <v>2</v>
+      </c>
+      <c r="R9" s="6">
+        <v>3</v>
+      </c>
       <c r="S9" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="T9" s="6">
+        <v>3</v>
+      </c>
+      <c r="U9" s="6">
+        <v>4</v>
+      </c>
+      <c r="V9" s="6">
+        <v>2</v>
+      </c>
+      <c r="W9" s="6">
+        <v>3</v>
+      </c>
+      <c r="X9" s="6">
+        <v>3</v>
+      </c>
       <c r="Y9" s="6">
         <v>-6</v>
       </c>
       <c r="Z9" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="AA9" s="7">
         <f t="shared" si="4"/>
@@ -1310,19 +1518,19 @@
       </c>
       <c r="AB9" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC9" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD9" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>9</v>
       </c>
       <c r="AE9" s="11">
         <f t="shared" si="8"/>
-        <v>-9.4</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
@@ -1346,35 +1554,65 @@
         <f t="shared" si="0"/>
         <v>-6.3</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="H10" s="6">
+        <v>2</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1</v>
+      </c>
+      <c r="J10" s="6">
+        <v>2</v>
+      </c>
+      <c r="K10" s="6">
+        <v>3</v>
+      </c>
       <c r="L10" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M10" s="6">
+        <v>3</v>
+      </c>
+      <c r="N10" s="6">
+        <v>5</v>
+      </c>
+      <c r="O10" s="6">
+        <v>4</v>
+      </c>
+      <c r="P10" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>2</v>
+      </c>
+      <c r="R10" s="6">
+        <v>3</v>
+      </c>
       <c r="S10" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6"/>
+        <v>20</v>
+      </c>
+      <c r="T10" s="6">
+        <v>2</v>
+      </c>
+      <c r="U10" s="6">
+        <v>2</v>
+      </c>
+      <c r="V10" s="6">
+        <v>3</v>
+      </c>
+      <c r="W10" s="6">
+        <v>3</v>
+      </c>
+      <c r="X10" s="6">
+        <v>3</v>
+      </c>
       <c r="Y10" s="6">
         <v>-6</v>
       </c>
       <c r="Z10" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="7">
         <f t="shared" si="4"/>
@@ -1382,19 +1620,19 @@
       </c>
       <c r="AB10" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC10" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AD10" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AE10" s="11">
         <f t="shared" si="8"/>
-        <v>-12.3</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
@@ -1418,35 +1656,65 @@
         <f t="shared" si="0"/>
         <v>-4.8000000000000007</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="H11" s="6">
+        <v>2</v>
+      </c>
+      <c r="I11" s="6">
+        <v>2</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6">
+        <v>2</v>
+      </c>
       <c r="L11" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="M11" s="6">
+        <v>2</v>
+      </c>
+      <c r="N11" s="6">
+        <v>1</v>
+      </c>
+      <c r="O11" s="6">
+        <v>4</v>
+      </c>
+      <c r="P11" s="6">
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>2</v>
+      </c>
+      <c r="R11" s="6">
+        <v>2</v>
+      </c>
       <c r="S11" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-      <c r="V11" s="6"/>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
+        <v>13</v>
+      </c>
+      <c r="T11" s="6">
+        <v>2</v>
+      </c>
+      <c r="U11" s="6">
+        <v>3</v>
+      </c>
+      <c r="V11" s="6">
+        <v>2</v>
+      </c>
+      <c r="W11" s="6">
+        <v>3</v>
+      </c>
+      <c r="X11" s="6">
+        <v>2</v>
+      </c>
       <c r="Y11" s="6">
         <v>-6</v>
       </c>
       <c r="Z11" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" si="4"/>
@@ -1454,19 +1722,19 @@
       </c>
       <c r="AB11" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC11" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD11" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>6</v>
       </c>
       <c r="AE11" s="11">
         <f t="shared" si="8"/>
-        <v>-10.8</v>
+        <v>21.2</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
@@ -1490,35 +1758,65 @@
         <f t="shared" si="0"/>
         <v>-7.1999999999999993</v>
       </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="H12" s="6">
+        <v>2</v>
+      </c>
+      <c r="I12" s="6">
+        <v>2</v>
+      </c>
+      <c r="J12" s="6">
+        <v>1</v>
+      </c>
+      <c r="K12" s="6">
+        <v>3</v>
+      </c>
       <c r="L12" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M12" s="6">
+        <v>2</v>
+      </c>
+      <c r="N12" s="6">
+        <v>2</v>
+      </c>
+      <c r="O12" s="6">
+        <v>4</v>
+      </c>
+      <c r="P12" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>2</v>
+      </c>
+      <c r="R12" s="6">
+        <v>3</v>
+      </c>
       <c r="S12" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6"/>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6"/>
+        <v>16</v>
+      </c>
+      <c r="T12" s="6">
+        <v>2</v>
+      </c>
+      <c r="U12" s="6">
+        <v>2</v>
+      </c>
+      <c r="V12" s="6">
+        <v>3</v>
+      </c>
+      <c r="W12" s="6">
+        <v>3</v>
+      </c>
+      <c r="X12" s="6">
+        <v>3</v>
+      </c>
       <c r="Y12" s="6">
         <v>-6</v>
       </c>
       <c r="Z12" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="7">
         <f t="shared" si="4"/>
@@ -1526,19 +1824,19 @@
       </c>
       <c r="AB12" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC12" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD12" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="AE12" s="11">
         <f t="shared" si="8"/>
-        <v>-13.2</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
@@ -1562,35 +1860,65 @@
         <f t="shared" si="0"/>
         <v>0.69999999999999973</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="H13" s="6">
+        <v>2</v>
+      </c>
+      <c r="I13" s="6">
+        <v>2</v>
+      </c>
+      <c r="J13" s="6">
+        <v>2</v>
+      </c>
+      <c r="K13" s="6">
+        <v>2</v>
+      </c>
       <c r="L13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M13" s="6">
+        <v>1</v>
+      </c>
+      <c r="N13" s="6">
+        <v>3</v>
+      </c>
+      <c r="O13" s="6">
+        <v>4</v>
+      </c>
+      <c r="P13" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>2</v>
+      </c>
+      <c r="R13" s="6">
+        <v>2</v>
+      </c>
       <c r="S13" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="T13" s="6">
+        <v>1</v>
+      </c>
+      <c r="U13" s="6">
+        <v>1</v>
+      </c>
+      <c r="V13" s="6">
+        <v>2</v>
+      </c>
+      <c r="W13" s="6">
+        <v>3</v>
+      </c>
+      <c r="X13" s="6">
+        <v>2</v>
+      </c>
       <c r="Y13" s="6">
         <v>-6</v>
       </c>
       <c r="Z13" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="AA13" s="7">
         <f t="shared" si="4"/>
@@ -1598,19 +1926,19 @@
       </c>
       <c r="AB13" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC13" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD13" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="AE13" s="11">
         <f t="shared" si="8"/>
-        <v>-5.3000000000000007</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
@@ -1634,35 +1962,65 @@
         <f t="shared" si="0"/>
         <v>-6.6999999999999993</v>
       </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="H14" s="6">
+        <v>2</v>
+      </c>
+      <c r="I14" s="6">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <v>2</v>
+      </c>
+      <c r="K14" s="6">
+        <v>2</v>
+      </c>
       <c r="L14" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="M14" s="6">
+        <v>2</v>
+      </c>
+      <c r="N14" s="6">
+        <v>3</v>
+      </c>
+      <c r="O14" s="6">
+        <v>4</v>
+      </c>
+      <c r="P14" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>2</v>
+      </c>
+      <c r="R14" s="6">
+        <v>3</v>
+      </c>
       <c r="S14" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
+        <v>17</v>
+      </c>
+      <c r="T14" s="6">
+        <v>2</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2</v>
+      </c>
+      <c r="V14" s="6">
+        <v>2</v>
+      </c>
+      <c r="W14" s="6">
+        <v>3</v>
+      </c>
+      <c r="X14" s="6">
+        <v>2</v>
+      </c>
       <c r="Y14" s="6">
         <v>-6</v>
       </c>
       <c r="Z14" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="7">
         <f t="shared" si="4"/>
@@ -1670,19 +2028,19 @@
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC14" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD14" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>5</v>
       </c>
       <c r="AE14" s="11">
         <f t="shared" si="8"/>
-        <v>-12.7</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
@@ -1706,35 +2064,65 @@
         <f t="shared" si="0"/>
         <v>-4.7</v>
       </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="H15" s="6">
+        <v>2</v>
+      </c>
+      <c r="I15" s="6">
+        <v>3</v>
+      </c>
+      <c r="J15" s="6">
+        <v>2</v>
+      </c>
+      <c r="K15" s="6">
+        <v>1</v>
+      </c>
       <c r="L15" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="M15" s="6">
+        <v>2</v>
+      </c>
+      <c r="N15" s="6">
+        <v>3</v>
+      </c>
+      <c r="O15" s="6">
+        <v>4</v>
+      </c>
+      <c r="P15" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>1</v>
+      </c>
+      <c r="R15" s="6">
+        <v>2</v>
+      </c>
       <c r="S15" s="9">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6"/>
+        <v>15</v>
+      </c>
+      <c r="T15" s="6">
+        <v>2</v>
+      </c>
+      <c r="U15" s="6">
+        <v>1</v>
+      </c>
+      <c r="V15" s="6">
+        <v>2</v>
+      </c>
+      <c r="W15" s="6">
+        <v>3</v>
+      </c>
+      <c r="X15" s="6">
+        <v>1</v>
+      </c>
       <c r="Y15" s="6">
         <v>-6</v>
       </c>
       <c r="Z15" s="10">
         <f t="shared" si="3"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" si="4"/>
@@ -1742,32 +2130,32 @@
       </c>
       <c r="AB15" s="8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC15" s="9">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AD15" s="10">
         <f t="shared" si="7"/>
-        <v>-6</v>
+        <v>3</v>
       </c>
       <c r="AE15" s="11">
         <f t="shared" si="8"/>
-        <v>-10.7</v>
+        <v>21.3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="AA1:AE1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="M1:S1"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="T1:Z1"/>
-    <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reiting1.xlsx
+++ b/reiting1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F2AE86-A0CC-4625-8EA1-69AB52381876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18C8101E-E8E1-49B6-B406-3C84628CD198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="1770" windowWidth="16365" windowHeight="10695" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
+    <workbookView xWindow="3345" yWindow="0" windowWidth="16365" windowHeight="10695" xr2:uid="{65B562F7-4CCD-46A4-AA6C-D53DA83FA9FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Predmet" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <t>МОМЫНОВ Қуат</t>
   </si>
   <si>
-    <t>Ср балл по предмету</t>
-  </si>
-  <si>
     <t>кол-во итоговых троек</t>
   </si>
   <si>
@@ -177,10 +174,13 @@
     <t>Итог метод. деятельности</t>
   </si>
   <si>
-    <t>Коэф предмета</t>
-  </si>
-  <si>
     <t>номер</t>
+  </si>
+  <si>
+    <t>Коэф</t>
+  </si>
+  <si>
+    <t>Ср балл</t>
   </si>
 </sst>
 </file>
@@ -666,7 +666,7 @@
   <sheetData>
     <row r="1" spans="1:32" s="1" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>0</v>
@@ -678,49 +678,49 @@
         <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>38</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
       <c r="N1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>49</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>9</v>

--- a/reiting1.xlsx
+++ b/reiting1.xlsx
@@ -1,87 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Загрузка\reiting-main\reiting-main\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21885" windowHeight="11940"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t>ФИО</t>
-  </si>
-  <si>
-    <t>Предмет</t>
-  </si>
-  <si>
-    <t>Коэф</t>
-  </si>
-  <si>
-    <t>Ср.балл</t>
-  </si>
-  <si>
-    <t>Үштік</t>
-  </si>
-  <si>
-    <t>Результативность</t>
-  </si>
-  <si>
-    <t>Метод.</t>
-  </si>
-  <si>
-    <t>Админ.рейтинг</t>
-  </si>
-  <si>
-    <t>Жалпы итог</t>
-  </si>
-  <si>
-    <t>Математика</t>
-  </si>
-  <si>
-    <t>Химия</t>
-  </si>
-  <si>
-    <t>Учитель1</t>
-  </si>
-  <si>
-    <t>Учитель2</t>
-  </si>
-  <si>
-    <t>Учитель3</t>
-  </si>
-  <si>
-    <t>Работа с одаренными детьми.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -100,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -402,140 +408,535 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ФИО</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Коэф</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ср.балл</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Үштік</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Результативность</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Внеклас.</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Метод.</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Админ.рейтинг</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Жалпы итог</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>АХШАЛОВА</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>АЗЫМБАЕВА</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Химия</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="G3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>АЙТБАЙ</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>АЛЬМЕНОВА</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Русский язык</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>АЛЬНАЗИРОВА</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ин яз</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>АРЫНГАЗИНА</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Каз яз</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ИЛЬЯСОВА</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ин яз</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ИТЕМГЕНОВ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>история</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>КАБЫЛОВА</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Каз яз</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J10" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>КАЗАНГАПОВ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ин яз</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J11" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>КАЙДАРОВА</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>География</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>КОЖАГЕЛЬДИНОВА</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Математика</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>МОМЫНОВ Қуат</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Информатика</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="E14" t="n">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D2">
-        <v>4.3</v>
-      </c>
-      <c r="E2">
-        <v>11</v>
-      </c>
-      <c r="F2">
-        <v>-5.2</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>8</v>
-      </c>
-      <c r="J2">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>4.5</v>
-      </c>
-      <c r="E3">
-        <v>8</v>
-      </c>
-      <c r="F3">
-        <v>-2.7</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>7</v>
-      </c>
-      <c r="J3">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D4">
-        <v>4.7</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
+      <c r="F14" t="n">
         <v>-2.9</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>7</v>
-      </c>
-      <c r="J4">
-        <v>7.1</v>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>